--- a/docs/projet/Fiche_de_retours.xlsx
+++ b/docs/projet/Fiche_de_retours.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>EGUITRA GROUP SARLU et MB AxisPro Consulting · E-VOLUTION XP</t>
+          <t>EGUITRA GROUP SARLU et MB AxisPro · E-VOLUTION XP</t>
         </is>
       </c>
     </row>
